--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x13340451\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x13340451\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2EF02C2-DD13-42AA-8A68-C41BDA438ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="7200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -291,13 +290,19 @@
   </si>
   <si>
     <t>4.4.9.2</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios - Melhoria da oferta e do acesso à saúde em Unaí</t>
+  </si>
+  <si>
+    <t>Em criação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -774,9 +779,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -808,10 +816,10 @@
     <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
     <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Incorreto" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Neutra" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
@@ -1131,16 +1139,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D75"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="66.140625" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1154,7 +1162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9288130</v>
       </c>
@@ -1168,7 +1176,7 @@
         <v>450000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9288130</v>
       </c>
@@ -1182,7 +1190,7 @@
         <v>1195796000</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9288132</v>
       </c>
@@ -1196,7 +1204,7 @@
         <v>603000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9288133</v>
       </c>
@@ -1210,7 +1218,7 @@
         <v>1187000000</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9288134</v>
       </c>
@@ -1224,7 +1232,7 @@
         <v>140860000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9288135</v>
       </c>
@@ -1238,7 +1246,7 @@
         <v>1345000</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9288136</v>
       </c>
@@ -1252,7 +1260,7 @@
         <v>111480000</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9288137</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>98100000</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9288138</v>
       </c>
@@ -1280,7 +1288,7 @@
         <v>38614000</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9288139</v>
       </c>
@@ -1294,7 +1302,7 @@
         <v>4400000</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9288141</v>
       </c>
@@ -1308,7 +1316,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9288142</v>
       </c>
@@ -1319,10 +1327,10 @@
         <v>7</v>
       </c>
       <c r="D13" s="1">
-        <v>36712000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>40151506.979999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9288143</v>
       </c>
@@ -1336,7 +1344,7 @@
         <v>722675.44</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9288144</v>
       </c>
@@ -1350,7 +1358,7 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9288145</v>
       </c>
@@ -1364,7 +1372,7 @@
         <v>45345000</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9288147</v>
       </c>
@@ -1378,7 +1386,7 @@
         <v>14817323</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9288148</v>
       </c>
@@ -1392,7 +1400,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9288149</v>
       </c>
@@ -1406,7 +1414,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9288150</v>
       </c>
@@ -1420,7 +1428,7 @@
         <v>10650450</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9288152</v>
       </c>
@@ -1434,7 +1442,7 @@
         <v>15130000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9288153</v>
       </c>
@@ -1448,7 +1456,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9288154</v>
       </c>
@@ -1462,7 +1470,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9288155</v>
       </c>
@@ -1476,7 +1484,7 @@
         <v>5550438.4000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9288167</v>
       </c>
@@ -1490,7 +1498,7 @@
         <v>3773400</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9288168</v>
       </c>
@@ -1504,7 +1512,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9288169</v>
       </c>
@@ -1518,7 +1526,7 @@
         <v>16112602.23</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9288176</v>
       </c>
@@ -1532,7 +1540,7 @@
         <v>40729352.109999999</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9288177</v>
       </c>
@@ -1546,7 +1554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9288178</v>
       </c>
@@ -1560,7 +1568,7 @@
         <v>253000000</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9288179</v>
       </c>
@@ -1574,7 +1582,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9288180</v>
       </c>
@@ -1588,7 +1596,7 @@
         <v>3072030000</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9288181</v>
       </c>
@@ -1602,7 +1610,7 @@
         <v>75352000</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9288182</v>
       </c>
@@ -1616,7 +1624,7 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9288183</v>
       </c>
@@ -1630,7 +1638,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9288185</v>
       </c>
@@ -1644,7 +1652,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9288186</v>
       </c>
@@ -1658,7 +1666,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9288187</v>
       </c>
@@ -1672,7 +1680,7 @@
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9288188</v>
       </c>
@@ -1686,7 +1694,7 @@
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9288189</v>
       </c>
@@ -1700,7 +1708,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9288190</v>
       </c>
@@ -1714,7 +1722,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9288191</v>
       </c>
@@ -1728,7 +1736,7 @@
         <v>160773401.72</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9288192</v>
       </c>
@@ -1742,7 +1750,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9288193</v>
       </c>
@@ -1756,7 +1764,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9288194</v>
       </c>
@@ -1767,10 +1775,10 @@
         <v>7</v>
       </c>
       <c r="D45" s="1">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>160493.01999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9288195</v>
       </c>
@@ -1784,7 +1792,7 @@
         <v>749679</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9288196</v>
       </c>
@@ -1798,7 +1806,7 @@
         <v>42412000</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>9288198</v>
       </c>
@@ -1809,10 +1817,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="1">
-        <v>836059044</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
+        <v>796059044</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>9288210</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>2300000</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9288211</v>
       </c>
@@ -1840,7 +1848,7 @@
         <v>3400000</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9288212</v>
       </c>
@@ -1854,7 +1862,7 @@
         <v>2427295557.8899999</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9288213</v>
       </c>
@@ -1868,7 +1876,7 @@
         <v>23000005</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9321270</v>
       </c>
@@ -1882,7 +1890,7 @@
         <v>842212.06</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9334530</v>
       </c>
@@ -1896,7 +1904,7 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9337957</v>
       </c>
@@ -1910,7 +1918,7 @@
         <v>470156273.05000001</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9341846</v>
       </c>
@@ -1924,7 +1932,7 @@
         <v>13899715.810000001</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>9342884</v>
       </c>
@@ -1938,7 +1946,7 @@
         <v>51000000</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9345097</v>
       </c>
@@ -1952,7 +1960,7 @@
         <v>3091703.6</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>9345390</v>
       </c>
@@ -1966,7 +1974,7 @@
         <v>24164127.77</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>9361779</v>
       </c>
@@ -1980,7 +1988,7 @@
         <v>164460000</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>9395028</v>
       </c>
@@ -1994,7 +2002,7 @@
         <v>307500225.61000001</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>9428104</v>
       </c>
@@ -2008,7 +2016,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>9428110</v>
       </c>
@@ -2022,7 +2030,7 @@
         <v>200689167</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>9435581</v>
       </c>
@@ -2033,10 +2041,10 @@
         <v>7</v>
       </c>
       <c r="D64" s="1">
-        <v>402688785.73000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>402995175.74000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>9440688</v>
       </c>
@@ -2050,7 +2058,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>9447772</v>
       </c>
@@ -2064,7 +2072,7 @@
         <v>200000000</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>9447773</v>
       </c>
@@ -2078,7 +2086,7 @@
         <v>122491729.81999999</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>9468058</v>
       </c>
@@ -2092,7 +2100,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>9468204</v>
       </c>
@@ -2106,7 +2114,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9481527</v>
       </c>
@@ -2117,10 +2125,10 @@
         <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>72830000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>87800000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>9478733</v>
       </c>
@@ -2134,7 +2142,7 @@
         <v>4031040</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>9484137</v>
       </c>
@@ -2148,7 +2156,7 @@
         <v>10968960</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>9483933</v>
       </c>
@@ -2162,7 +2170,7 @@
         <v>29000000</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>9483938</v>
       </c>
@@ -2176,8 +2184,19 @@
         <v>67000000</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="D75" s="1"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="1">
+        <v>40000000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -1215,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>1187000000</v>
+        <v>1197850000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1999,7 +1999,7 @@
         <v>68</v>
       </c>
       <c r="D61" s="1">
-        <v>307500225.61000001</v>
+        <v>317500225.61000001</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">

--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>Melhoria da infraestrutura dos municípios - Melhoria da oferta e do acesso à saúde em Unaí</t>
-  </si>
-  <si>
-    <t>Em criação</t>
   </si>
 </sst>
 </file>
@@ -779,12 +776,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2125,7 +2119,7 @@
         <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>87800000</v>
+        <v>72830000</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -2185,8 +2179,8 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="2" t="s">
-        <v>85</v>
+      <c r="A75">
+        <v>9499616</v>
       </c>
       <c r="B75" t="s">
         <v>84</v>
@@ -2200,5 +2194,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -2007,7 +2007,7 @@
         <v>7</v>
       </c>
       <c r="D62" s="1">
-        <v>6000000</v>
+        <v>6100000</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2035,7 +2035,7 @@
         <v>7</v>
       </c>
       <c r="D64" s="1">
-        <v>402995175.74000001</v>
+        <v>402803870.00999999</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">

--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -2119,7 +2119,7 @@
         <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>72830000</v>
+        <v>87800000</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">

--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x13340451\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\Trabalho\AFPR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6030"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">in!$A$1:$D$75</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -157,9 +157,6 @@
     <t>Ampliação de postos de abastecimento próprios do Estado</t>
   </si>
   <si>
-    <t>Melhoria da estrutura logística e energética da Cidade Administrativa para redução de custos</t>
-  </si>
-  <si>
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
@@ -293,6 +290,9 @@
   </si>
   <si>
     <t>Melhoria da infraestrutura dos municípios - Melhoria da oferta e do acesso à saúde em Unaí</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura da Cidade Administrativa</t>
   </si>
 </sst>
 </file>
@@ -1134,11 +1134,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="66.140625" customWidth="1"/>
+    <col min="2" max="2" width="81.28515625" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1156,7 +1157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9288130</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>450000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9288130</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>1195796000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9288132</v>
       </c>
@@ -1198,7 +1199,7 @@
         <v>603000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9288133</v>
       </c>
@@ -1212,7 +1213,7 @@
         <v>1197850000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9288134</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>140860000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9288135</v>
       </c>
@@ -1237,10 +1238,10 @@
         <v>7</v>
       </c>
       <c r="D7" s="1">
-        <v>1345000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1229711.58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9288136</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>111480000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9288137</v>
       </c>
@@ -1268,7 +1269,7 @@
         <v>98100000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9288138</v>
       </c>
@@ -1282,7 +1283,7 @@
         <v>38614000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9288139</v>
       </c>
@@ -1296,7 +1297,7 @@
         <v>4400000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9288141</v>
       </c>
@@ -1310,7 +1311,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9288142</v>
       </c>
@@ -1324,7 +1325,7 @@
         <v>40151506.979999997</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9288143</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>722675.44</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9288144</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9288145</v>
       </c>
@@ -1366,7 +1367,7 @@
         <v>45345000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9288147</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>14817323</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9288148</v>
       </c>
@@ -1394,7 +1395,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9288149</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9288150</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>10650450</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9288152</v>
       </c>
@@ -1436,7 +1437,7 @@
         <v>15130000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9288153</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9288154</v>
       </c>
@@ -1464,7 +1465,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9288155</v>
       </c>
@@ -1478,7 +1479,7 @@
         <v>5550438.4000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9288167</v>
       </c>
@@ -1489,10 +1490,10 @@
         <v>7</v>
       </c>
       <c r="D25" s="1">
-        <v>3773400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3773214.87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9288168</v>
       </c>
@@ -1506,7 +1507,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9288169</v>
       </c>
@@ -1520,7 +1521,7 @@
         <v>16112602.23</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9288176</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>40729352.109999999</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9288177</v>
       </c>
@@ -1548,7 +1549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9288178</v>
       </c>
@@ -1562,7 +1563,7 @@
         <v>253000000</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9288179</v>
       </c>
@@ -1576,7 +1577,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9288180</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>3072030000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9288181</v>
       </c>
@@ -1604,7 +1605,7 @@
         <v>75352000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9288182</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
@@ -1632,12 +1633,12 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
         <v>7</v>
@@ -1646,12 +1647,12 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1660,12 +1661,12 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -1674,12 +1675,12 @@
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -1688,12 +1689,12 @@
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -1702,54 +1703,54 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D41" s="1">
         <v>100000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
         <v>46</v>
-      </c>
-      <c r="C42" t="s">
-        <v>47</v>
       </c>
       <c r="D42" s="1">
         <v>160773401.72</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1">
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
         <v>7</v>
@@ -1758,12 +1759,12 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
@@ -1772,12 +1773,12 @@
         <v>160493.01999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
@@ -1786,12 +1787,12 @@
         <v>749679</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -1800,12 +1801,12 @@
         <v>42412000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
@@ -1814,54 +1815,54 @@
         <v>796059044</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>9288210</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="1">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2069341.81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9288211</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="1">
-        <v>3400000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3342402.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9288212</v>
       </c>
       <c r="B51" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" t="s">
         <v>56</v>
-      </c>
-      <c r="C51" t="s">
-        <v>57</v>
       </c>
       <c r="D51" s="1">
         <v>2427295557.8899999</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9288213</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
         <v>7</v>
@@ -1870,12 +1871,12 @@
         <v>23000005</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9321270</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
@@ -1884,12 +1885,12 @@
         <v>842212.06</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9334530</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
@@ -1898,12 +1899,12 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9337957</v>
       </c>
       <c r="B55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1912,12 +1913,12 @@
         <v>470156273.05000001</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9341846</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
@@ -1926,12 +1927,12 @@
         <v>13899715.810000001</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>9342884</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
         <v>7</v>
@@ -1940,12 +1941,12 @@
         <v>51000000</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9345097</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C58" t="s">
         <v>7</v>
@@ -1954,12 +1955,12 @@
         <v>3091703.6</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>9345390</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
@@ -1968,12 +1969,12 @@
         <v>24164127.77</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>9361779</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1982,26 +1983,26 @@
         <v>164460000</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>9395028</v>
       </c>
       <c r="B61" t="s">
+        <v>66</v>
+      </c>
+      <c r="C61" t="s">
         <v>67</v>
-      </c>
-      <c r="C61" t="s">
-        <v>68</v>
       </c>
       <c r="D61" s="1">
         <v>317500225.61000001</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>9428104</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C62" t="s">
         <v>7</v>
@@ -2010,12 +2011,12 @@
         <v>6100000</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>9428110</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
         <v>7</v>
@@ -2024,12 +2025,12 @@
         <v>200689167</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>9435581</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C64" t="s">
         <v>7</v>
@@ -2038,12 +2039,12 @@
         <v>402803870.00999999</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>9440688</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
         <v>7</v>
@@ -2052,40 +2053,40 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>9447772</v>
       </c>
       <c r="B66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D66" s="1">
         <v>200000000</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>9447773</v>
       </c>
       <c r="B67" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" t="s">
         <v>74</v>
-      </c>
-      <c r="C67" t="s">
-        <v>75</v>
       </c>
       <c r="D67" s="1">
         <v>122491729.81999999</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>9468058</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C68" t="s">
         <v>7</v>
@@ -2094,12 +2095,12 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>9468204</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
         <v>7</v>
@@ -2108,82 +2109,82 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>9481527</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="1">
-        <v>87800000</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>142600000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>9478733</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="1">
-        <v>4031040</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8700000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>9484137</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C72" t="s">
         <v>7</v>
       </c>
       <c r="D72" s="1">
-        <v>10968960</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>9483933</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
         <v>7</v>
       </c>
       <c r="D73" s="1">
-        <v>29000000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22300000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>9483938</v>
       </c>
       <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" t="s">
         <v>82</v>
-      </c>
-      <c r="C74" t="s">
-        <v>83</v>
       </c>
       <c r="D74" s="1">
         <v>67000000</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>9499616</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
         <v>7</v>
@@ -2193,6 +2194,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D75">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Melhoria da estrutura logística e energética da Cidade Administrativa para redução de custos"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
